--- a/Attendance/DSA Batch ALL.xlsx
+++ b/Attendance/DSA Batch ALL.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765274E7-1376-4AF1-B948-E7853D81490B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7A8DF9-77D0-403B-B87A-D25F8BB6214B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="107">
   <si>
     <t>S. No.</t>
   </si>
@@ -323,6 +322,30 @@
   </si>
   <si>
     <t>14 Jul PM</t>
+  </si>
+  <si>
+    <t>15  Jul PM</t>
+  </si>
+  <si>
+    <t>Deveshri</t>
+  </si>
+  <si>
+    <t>Aaditi uday rane</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dhaanashree borkar</t>
+  </si>
+  <si>
+    <t>Aiml</t>
+  </si>
+  <si>
+    <t>ENTC</t>
+  </si>
+  <si>
+    <t>16 Jul PM</t>
   </si>
 </sst>
 </file>
@@ -675,13 +698,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8080B9-1F79-4EA3-BF5D-949EC22A7384}">
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -745,8 +769,14 @@
       <c r="U1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" t="s">
+        <v>99</v>
+      </c>
+      <c r="W1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -790,7 +820,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -834,7 +864,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -878,7 +908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -922,7 +952,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -966,7 +996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1015,8 +1045,17 @@
       <c r="R7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" t="s">
+        <v>49</v>
+      </c>
+      <c r="W7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1060,7 +1099,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1104,7 +1143,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1148,7 +1187,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1192,7 +1231,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1236,7 +1275,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1280,7 +1319,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1324,7 +1363,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1368,7 +1407,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1412,7 +1451,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1456,7 +1495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1499,11 +1538,8 @@
       <c r="P18" t="s">
         <v>52</v>
       </c>
-      <c r="U18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1547,7 +1583,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1597,7 +1633,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1641,7 +1677,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1687,8 +1723,14 @@
       <c r="U22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" t="s">
+        <v>49</v>
+      </c>
+      <c r="W22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1732,7 +1774,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1793,8 +1835,14 @@
       <c r="T24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>49</v>
+      </c>
+      <c r="W24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1849,8 +1897,14 @@
       <c r="T25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25" t="s">
+        <v>49</v>
+      </c>
+      <c r="W25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1894,7 +1948,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1947,7 +2001,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2005,8 +2059,14 @@
       <c r="U28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28" t="s">
+        <v>49</v>
+      </c>
+      <c r="W28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2059,7 +2119,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2114,8 +2174,14 @@
       <c r="T30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" t="s">
+        <v>49</v>
+      </c>
+      <c r="W30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2171,7 +2237,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2215,7 +2281,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2264,8 +2330,14 @@
       <c r="U33" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" t="s">
+        <v>49</v>
+      </c>
+      <c r="W33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2309,7 +2381,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2350,7 +2422,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2394,7 +2466,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2438,7 +2510,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2482,7 +2554,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2531,8 +2603,14 @@
       <c r="U39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39" t="s">
+        <v>49</v>
+      </c>
+      <c r="W39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2579,7 +2657,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2626,7 +2704,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2667,7 +2745,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2708,7 +2786,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2758,7 +2836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2796,7 +2874,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2834,7 +2912,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2872,7 +2950,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2924,8 +3002,17 @@
       <c r="R48" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U48" t="s">
+        <v>49</v>
+      </c>
+      <c r="V48" t="s">
+        <v>49</v>
+      </c>
+      <c r="W48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2966,7 +3053,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3012,8 +3099,14 @@
       <c r="U50" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50" t="s">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3068,8 +3161,14 @@
       <c r="T51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51" t="s">
+        <v>49</v>
+      </c>
+      <c r="W51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3112,8 +3211,14 @@
       <c r="P52" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52" t="s">
+        <v>49</v>
+      </c>
+      <c r="W52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3156,8 +3261,14 @@
       <c r="P53" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53" t="s">
+        <v>49</v>
+      </c>
+      <c r="W53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3209,8 +3320,14 @@
       <c r="U54" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54" t="s">
+        <v>49</v>
+      </c>
+      <c r="W54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3227,7 +3344,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3241,6 +3358,60 @@
         <v>97</v>
       </c>
       <c r="U56" t="s">
+        <v>49</v>
+      </c>
+      <c r="V56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57">
+        <v>241102077</v>
+      </c>
+      <c r="E57" t="s">
+        <v>105</v>
+      </c>
+      <c r="W57" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="C58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58">
+        <v>241101191</v>
+      </c>
+      <c r="E58" t="s">
+        <v>102</v>
+      </c>
+      <c r="W58" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59">
+        <v>241107065</v>
+      </c>
+      <c r="E59" t="s">
+        <v>104</v>
+      </c>
+      <c r="W59" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3250,13 +3421,4 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDB9BCD-5898-4A00-9D2B-1EB90A88F4B9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Attendance/DSA Batch ALL.xlsx
+++ b/Attendance/DSA Batch ALL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7A8DF9-77D0-403B-B87A-D25F8BB6214B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05263D7E-92D8-474D-8A10-F4DD7DCDD779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="109">
   <si>
     <t>S. No.</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>16 Jul PM</t>
+  </si>
+  <si>
+    <t>17 Jul PM</t>
+  </si>
+  <si>
+    <t>18 Jul PM</t>
   </si>
 </sst>
 </file>
@@ -698,14 +704,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8080B9-1F79-4EA3-BF5D-949EC22A7384}">
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -775,8 +781,14 @@
       <c r="W1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -820,7 +832,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -864,7 +876,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -908,7 +920,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -952,7 +964,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -996,7 +1008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1055,7 +1067,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1099,7 +1111,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1143,7 +1155,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1187,7 +1199,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1231,7 +1243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1275,7 +1287,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1319,7 +1331,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1363,7 +1375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1407,7 +1419,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1451,7 +1463,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1495,7 +1507,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1539,7 +1551,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1583,7 +1595,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1632,8 +1644,11 @@
       <c r="P20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1677,7 +1692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1729,8 +1744,14 @@
       <c r="W22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1774,7 +1795,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1841,8 +1862,14 @@
       <c r="W24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1903,8 +1930,14 @@
       <c r="W25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1948,7 +1981,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2001,7 +2034,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2065,8 +2098,14 @@
       <c r="W28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2119,7 +2158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2180,8 +2219,14 @@
       <c r="W30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2237,7 +2282,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2281,7 +2326,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2336,8 +2381,11 @@
       <c r="W33" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2381,7 +2429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2422,7 +2470,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2466,7 +2514,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2510,7 +2558,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2554,7 +2602,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2609,8 +2657,11 @@
       <c r="W39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2657,7 +2708,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2703,8 +2754,14 @@
       <c r="P41" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2745,7 +2802,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2786,7 +2843,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2835,8 +2892,11 @@
       <c r="S44" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2874,7 +2934,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2912,7 +2972,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2950,7 +3010,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3011,8 +3071,14 @@
       <c r="W48" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3053,7 +3119,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3105,8 +3171,14 @@
       <c r="W50" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3167,8 +3239,14 @@
       <c r="W51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3218,7 +3296,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3268,7 +3346,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3327,7 +3405,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3344,7 +3422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3364,7 +3442,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3381,7 +3459,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3398,7 +3476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>

--- a/Attendance/DSA Batch ALL.xlsx
+++ b/Attendance/DSA Batch ALL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05263D7E-92D8-474D-8A10-F4DD7DCDD779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C5C6D2-2ABD-453E-A682-25ACBC795024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="114">
   <si>
     <t>S. No.</t>
   </si>
@@ -352,6 +352,21 @@
   </si>
   <si>
     <t>18 Jul PM</t>
+  </si>
+  <si>
+    <t>20 Jul PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vikas Kachave</t>
+  </si>
+  <si>
+    <t>Ruchita Mali</t>
+  </si>
+  <si>
+    <t>21 Jul PM</t>
+  </si>
+  <si>
+    <t>Vaibhavi Rajenra nere</t>
   </si>
 </sst>
 </file>
@@ -704,14 +719,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8080B9-1F79-4EA3-BF5D-949EC22A7384}">
-  <dimension ref="A1:Y59"/>
+  <dimension ref="A1:AA62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -787,8 +802,14 @@
       <c r="Y1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -832,7 +853,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -876,7 +897,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -920,7 +941,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -964,7 +985,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1008,7 +1029,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1066,8 +1087,11 @@
       <c r="W7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1111,7 +1135,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1155,7 +1179,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1199,7 +1223,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1243,7 +1267,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1287,7 +1311,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1331,7 +1355,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1375,7 +1399,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1419,7 +1443,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1463,7 +1487,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1507,7 +1531,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1551,7 +1575,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1595,7 +1619,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1648,7 +1672,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1692,7 +1716,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1750,8 +1774,11 @@
       <c r="Y22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1795,7 +1822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1868,8 +1895,14 @@
       <c r="Y24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z24" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1936,8 +1969,14 @@
       <c r="Y25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1981,7 +2020,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2033,8 +2072,11 @@
       <c r="Q27" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2104,8 +2146,14 @@
       <c r="Y28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2157,8 +2205,11 @@
       <c r="Q29" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2225,8 +2276,11 @@
       <c r="Y30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2282,7 +2336,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2326,7 +2380,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2385,7 +2439,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2429,7 +2483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2470,7 +2524,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2514,7 +2568,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2558,7 +2612,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2602,7 +2656,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2661,7 +2715,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2708,7 +2762,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2760,8 +2814,14 @@
       <c r="Y41" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2802,7 +2862,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2843,7 +2903,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2896,7 +2956,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2934,7 +2994,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2972,7 +3032,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3010,7 +3070,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3077,8 +3137,14 @@
       <c r="Y48" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3119,7 +3185,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3178,7 +3244,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3245,8 +3311,11 @@
       <c r="Y51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3296,7 +3365,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3346,7 +3415,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3405,7 +3474,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3422,7 +3491,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3442,7 +3511,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3459,7 +3528,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3476,7 +3545,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3490,6 +3559,48 @@
         <v>104</v>
       </c>
       <c r="W59" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="C60" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="C61" t="s">
+        <v>111</v>
+      </c>
+      <c r="E61" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA62" t="s">
         <v>49</v>
       </c>
     </row>
